--- a/data/trans_dic/P0902-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P0902-Habitat-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que dejó de hacer algunas tareas por problemas físicos</t>
+          <t>Población que dejó de hacer algunas tareas por problemas físicos (tasa de respuesta: 99,96%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,79; 9,68</t>
+          <t>5,68; 9,75</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,61; 14,59</t>
+          <t>9,82; 14,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,19; 14,32</t>
+          <t>9,05; 14,04</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11,59; 16,94</t>
+          <t>11,64; 16,95</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,18; 12,73</t>
+          <t>8,3; 13,1</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,99; 24,02</t>
+          <t>17,63; 24,16</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,26; 25,8</t>
+          <t>19,08; 25,55</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>16,96; 21,47</t>
+          <t>17,05; 21,61</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,63; 10,61</t>
+          <t>7,68; 10,54</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14,55; 18,77</t>
+          <t>14,61; 18,67</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15,1; 19,06</t>
+          <t>15,11; 19,31</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>15,06; 18,77</t>
+          <t>15,03; 18,71</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,55; 10,12</t>
+          <t>6,58; 10,2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,98; 14,28</t>
+          <t>9,95; 14,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,53; 10,95</t>
+          <t>7,44; 10,97</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5,03; 12,02</t>
+          <t>4,89; 12,05</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,49; 15,77</t>
+          <t>11,57; 16,2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,42; 24,75</t>
+          <t>19,58; 24,97</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,2; 19,34</t>
+          <t>14,15; 19,24</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>17,56; 21,54</t>
+          <t>17,58; 21,94</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,41; 12,32</t>
+          <t>9,51; 12,44</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15,32; 18,71</t>
+          <t>15,34; 18,7</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11,37; 14,48</t>
+          <t>11,38; 14,5</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>9,15; 16,0</t>
+          <t>8,58; 15,93</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,66; 11,24</t>
+          <t>6,87; 11,1</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,66; 11,24</t>
+          <t>6,67; 11,35</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,5; 9,49</t>
+          <t>5,48; 9,41</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11,53; 16,78</t>
+          <t>11,61; 16,77</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14,27; 19,86</t>
+          <t>14,09; 19,89</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14,75; 20,23</t>
+          <t>14,85; 20,43</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,63; 19,11</t>
+          <t>13,6; 19,03</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>7,75; 19,18</t>
+          <t>6,69; 19,1</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11,06; 14,61</t>
+          <t>10,96; 14,6</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11,34; 14,97</t>
+          <t>11,39; 15,08</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10,23; 13,59</t>
+          <t>10,17; 13,71</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,1; 16,62</t>
+          <t>9,61; 16,78</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,38; 9,89</t>
+          <t>6,56; 9,96</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,04; 13,56</t>
+          <t>9,05; 13,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,65; 11,62</t>
+          <t>7,74; 11,68</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,39; 14,38</t>
+          <t>10,26; 14,45</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>14,89; 19,6</t>
+          <t>14,59; 19,55</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,66; 21,67</t>
+          <t>16,72; 21,79</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,48; 19,59</t>
+          <t>14,37; 19,48</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>16,0; 22,12</t>
+          <t>16,07; 22,37</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>11,12; 14,16</t>
+          <t>11,33; 14,24</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13,66; 16,84</t>
+          <t>13,68; 16,97</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11,94; 15,09</t>
+          <t>11,74; 15,04</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14,25; 18,01</t>
+          <t>14,38; 17,97</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,29; 9,22</t>
+          <t>7,28; 9,27</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,97; 12,19</t>
+          <t>9,89; 12,2</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,28; 10,28</t>
+          <t>8,36; 10,37</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9,29; 13,33</t>
+          <t>9,01; 13,24</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>13,37; 15,84</t>
+          <t>13,38; 15,79</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,73; 21,28</t>
+          <t>18,64; 21,4</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,5; 19,19</t>
+          <t>16,44; 19,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>14,43; 19,78</t>
+          <t>14,74; 19,81</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10,73; 12,26</t>
+          <t>10,69; 12,26</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14,61; 16,43</t>
+          <t>14,78; 16,42</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12,75; 14,44</t>
+          <t>12,75; 14,43</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,06; 16,21</t>
+          <t>13,25; 16,4</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1387,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que dejó de hacer algunas tareas por problemas físicos</t>
+          <t>Población que dejó de hacer algunas tareas por problemas físicos (tasa de respuesta: 99,96%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>40184; 67162</t>
+          <t>39399; 67667</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>67588; 102663</t>
+          <t>69057; 104763</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>61994; 96648</t>
+          <t>61081; 94755</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>73620; 107548</t>
+          <t>73915; 107652</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>56330; 87657</t>
+          <t>57137; 90161</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>125377; 167445</t>
+          <t>122883; 168388</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>129611; 173577</t>
+          <t>128406; 171943</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>114522; 144998</t>
+          <t>115093; 145884</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>105518; 146654</t>
+          <t>106113; 145702</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>203730; 262814</t>
+          <t>204677; 261477</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>203512; 256849</t>
+          <t>203657; 260219</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>197316; 245857</t>
+          <t>196972; 245174</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>63026; 97367</t>
+          <t>63248; 98109</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>101460; 145200</t>
+          <t>101218; 143052</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>76941; 111938</t>
+          <t>76029; 112139</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>59917; 143294</t>
+          <t>58269; 143704</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>111302; 152752</t>
+          <t>112047; 156901</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>200200; 255156</t>
+          <t>201906; 257420</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>148076; 201742</t>
+          <t>147532; 200621</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>168065; 206129</t>
+          <t>168230; 210011</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>181695; 237708</t>
+          <t>183625; 240038</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>313692; 383264</t>
+          <t>314211; 382911</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>234864; 299154</t>
+          <t>234936; 299486</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>196705; 343850</t>
+          <t>184416; 342421</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>45212; 76294</t>
+          <t>46581; 75297</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>50469; 85171</t>
+          <t>50514; 86000</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>41766; 72119</t>
+          <t>41628; 71482</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>81236; 118244</t>
+          <t>81793; 118209</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>97616; 135785</t>
+          <t>96326; 135994</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>114323; 156813</t>
+          <t>115156; 158392</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>107018; 150017</t>
+          <t>106797; 149362</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>72348; 179040</t>
+          <t>62422; 178236</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>150738; 198983</t>
+          <t>149259; 198927</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>173843; 229530</t>
+          <t>174589; 231208</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>158018; 209970</t>
+          <t>157153; 211835</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>149138; 272182</t>
+          <t>157397; 274834</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>60121; 93184</t>
+          <t>61853; 93887</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>85671; 128485</t>
+          <t>85772; 126712</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>71687; 108958</t>
+          <t>72586; 109510</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>96092; 133008</t>
+          <t>94925; 133722</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>154670; 203552</t>
+          <t>151499; 203084</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>175056; 227697</t>
+          <t>175725; 229037</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>151163; 204464</t>
+          <t>149940; 203338</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>175171; 242236</t>
+          <t>175982; 244957</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>220348; 280389</t>
+          <t>224388; 282037</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>273032; 336543</t>
+          <t>273442; 339116</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>236543; 299042</t>
+          <t>232525; 297930</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>287772; 363778</t>
+          <t>290420; 362953</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>238988; 302230</t>
+          <t>238484; 303784</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>341647; 417602</t>
+          <t>338801; 417786</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>281101; 349067</t>
+          <t>283906; 351962</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>321017; 460924</t>
+          <t>311360; 457551</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>451936; 535285</t>
+          <t>452227; 533460</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>665859; 756351</t>
+          <t>662615; 760522</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>584959; 680069</t>
+          <t>582595; 673586</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>528351; 724086</t>
+          <t>539522; 725184</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>713886; 816233</t>
+          <t>711231; 815883</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1019635; 1146997</t>
+          <t>1031353; 1146398</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>884783; 1002133</t>
+          <t>884720; 1001150</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>929269; 1153476</t>
+          <t>943159; 1167569</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P0902-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P0902-Habitat-trans_dic.xlsx
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,67%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,68; 9,75</t>
+          <t>5,62; 9,51</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,82; 14,89</t>
+          <t>9,57; 14,57</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,05; 14,04</t>
+          <t>8,99; 13,91</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11,64; 16,95</t>
+          <t>11,46; 16,58</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>8,3; 13,1</t>
+          <t>8,31; 12,81</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,63; 24,16</t>
+          <t>17,99; 24,26</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,08; 25,55</t>
+          <t>18,93; 25,51</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>17,05; 21,61</t>
+          <t>17,18; 21,62</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,68; 10,54</t>
+          <t>7,61; 10,43</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14,61; 18,67</t>
+          <t>14,37; 18,51</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>15,11; 19,31</t>
+          <t>14,88; 19,07</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>15,03; 18,71</t>
+          <t>14,92; 18,61</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,55%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>15,4%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,58; 10,2</t>
+          <t>6,57; 10,15</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,95; 14,07</t>
+          <t>9,91; 14,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,44; 10,97</t>
+          <t>7,43; 11,39</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,89; 12,05</t>
+          <t>9,36; 13,19</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>11,57; 16,2</t>
+          <t>11,17; 15,79</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,58; 24,97</t>
+          <t>19,73; 24,97</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>14,15; 19,24</t>
+          <t>14,12; 18,94</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>17,58; 21,94</t>
+          <t>17,62; 21,59</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,51; 12,44</t>
+          <t>9,58; 12,39</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15,34; 18,7</t>
+          <t>15,42; 18,85</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11,38; 14,5</t>
+          <t>11,37; 14,38</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,58; 15,93</t>
+          <t>14,1; 17,0</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>18,94%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>16,16%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,87; 11,1</t>
+          <t>6,72; 11,09</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,67; 11,35</t>
+          <t>6,73; 11,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,48; 9,41</t>
+          <t>5,52; 9,49</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11,61; 16,77</t>
+          <t>11,11; 16,22</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>14,09; 19,89</t>
+          <t>14,11; 19,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14,85; 20,43</t>
+          <t>14,86; 20,14</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>13,6; 19,03</t>
+          <t>13,7; 19,11</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>6,69; 19,1</t>
+          <t>16,81; 21,53</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10,96; 14,6</t>
+          <t>11,13; 14,81</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>11,39; 15,08</t>
+          <t>11,45; 14,88</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>10,17; 13,71</t>
+          <t>10,19; 13,49</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9,61; 16,78</t>
+          <t>14,6; 18,04</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,61%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,56; 9,96</t>
+          <t>6,42; 9,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>9,05; 13,37</t>
+          <t>9,18; 13,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,74; 11,68</t>
+          <t>7,92; 11,77</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,26; 14,45</t>
+          <t>10,13; 14,03</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>14,59; 19,55</t>
+          <t>14,63; 19,44</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>16,72; 21,79</t>
+          <t>16,62; 21,48</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,37; 19,48</t>
+          <t>14,47; 19,58</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>16,07; 22,37</t>
+          <t>18,77; 22,76</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>11,33; 14,24</t>
+          <t>11,3; 14,29</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>13,68; 16,97</t>
+          <t>13,64; 17,05</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>11,74; 15,04</t>
+          <t>11,87; 15,14</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14,38; 17,97</t>
+          <t>15,23; 17,93</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>18,13%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>16,17%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>7,28; 9,27</t>
+          <t>7,31; 9,16</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,89; 12,2</t>
+          <t>9,89; 12,18</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,36; 10,37</t>
+          <t>8,32; 10,32</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>9,01; 13,24</t>
+          <t>11,4; 13,63</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>13,38; 15,79</t>
+          <t>13,43; 15,85</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,64; 21,4</t>
+          <t>18,55; 21,26</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>16,44; 19,0</t>
+          <t>16,32; 19,18</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>14,74; 19,81</t>
+          <t>18,61; 20,75</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10,69; 12,26</t>
+          <t>10,71; 12,25</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14,78; 16,42</t>
+          <t>14,69; 16,43</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12,75; 14,43</t>
+          <t>12,64; 14,46</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,25; 16,4</t>
+          <t>15,37; 16,99</t>
         </is>
       </c>
     </row>
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>89445</t>
+          <t>97235</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>129963</t>
+          <t>139934</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>219408</t>
+          <t>237169</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>39399; 67667</t>
+          <t>39029; 66031</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>69057; 104763</t>
+          <t>67343; 102510</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>61081; 94755</t>
+          <t>60694; 93837</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>73915; 107652</t>
+          <t>79115; 114455</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>57137; 90161</t>
+          <t>57178; 88144</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>122883; 168388</t>
+          <t>125417; 169112</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>128406; 171943</t>
+          <t>127384; 171638</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>115093; 145884</t>
+          <t>125876; 158404</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>106113; 145702</t>
+          <t>105209; 144243</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>204677; 261477</t>
+          <t>201315; 259211</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>203657; 260219</t>
+          <t>200503; 256969</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>196972; 245174</t>
+          <t>212232; 264711</t>
         </is>
       </c>
     </row>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>107385</t>
+          <t>116869</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>186022</t>
+          <t>209143</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>293407</t>
+          <t>326012</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>63248; 98109</t>
+          <t>63193; 97608</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>101218; 143052</t>
+          <t>100749; 143882</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>76029; 112139</t>
+          <t>75984; 116453</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>58269; 143704</t>
+          <t>98094; 138204</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>112047; 156901</t>
+          <t>108183; 152902</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>201906; 257420</t>
+          <t>203448; 257481</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>147532; 200621</t>
+          <t>147286; 197488</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>168230; 210011</t>
+          <t>188488; 230998</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>183625; 240038</t>
+          <t>184873; 239196</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>314211; 382911</t>
+          <t>315776; 386128</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>234936; 299486</t>
+          <t>234782; 297075</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>184416; 342421</t>
+          <t>298495; 359931</t>
         </is>
       </c>
     </row>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>98288</t>
+          <t>107238</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2028,7 +2028,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>132098</t>
+          <t>153825</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>230386</t>
+          <t>261063</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>46581; 75297</t>
+          <t>45583; 75278</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>50514; 86000</t>
+          <t>50971; 85471</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>41628; 71482</t>
+          <t>41936; 72077</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>81793; 118209</t>
+          <t>89233; 130256</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>96326; 135994</t>
+          <t>96498; 134180</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>115156; 158392</t>
+          <t>115183; 156157</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>106797; 149362</t>
+          <t>107575; 150047</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>62422; 178236</t>
+          <t>136518; 174911</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>149259; 198927</t>
+          <t>151623; 201774</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>174589; 231208</t>
+          <t>175556; 228158</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>157153; 211835</t>
+          <t>157317; 208378</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>157397; 274834</t>
+          <t>235776; 291454</t>
         </is>
       </c>
     </row>
@@ -2216,7 +2216,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>114387</t>
+          <t>118774</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>215445</t>
+          <t>231347</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>329832</t>
+          <t>350121</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>61853; 93887</t>
+          <t>60513; 92593</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>85772; 126712</t>
+          <t>86974; 126726</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>72586; 109510</t>
+          <t>74253; 110325</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>94925; 133722</t>
+          <t>100167; 138649</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>151499; 203084</t>
+          <t>151987; 201859</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>175725; 229037</t>
+          <t>174635; 225699</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>149940; 203338</t>
+          <t>151054; 204351</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>175982; 244957</t>
+          <t>210050; 254662</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>224388; 282037</t>
+          <t>223919; 283126</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>273442; 339116</t>
+          <t>272644; 340846</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>232525; 297930</t>
+          <t>235268; 300073</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>290420; 362953</t>
+          <t>320891; 377913</t>
         </is>
       </c>
     </row>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>409505</t>
+          <t>440116</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2444,7 +2444,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>663528</t>
+          <t>734249</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1073033</t>
+          <t>1174366</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>238484; 303784</t>
+          <t>239433; 300171</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>338801; 417786</t>
+          <t>338802; 417195</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>283906; 351962</t>
+          <t>282523; 350229</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>311360; 457551</t>
+          <t>402461; 481057</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>452227; 533460</t>
+          <t>453785; 535608</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>662615; 760522</t>
+          <t>659330; 755598</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>582595; 673586</t>
+          <t>578553; 679771</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>539522; 725184</t>
+          <t>694929; 774617</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>711231; 815883</t>
+          <t>712708; 815514</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1031353; 1146398</t>
+          <t>1025490; 1146875</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>884720; 1001150</t>
+          <t>877351; 1003038</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>943159; 1167569</t>
+          <t>1116300; 1233820</t>
         </is>
       </c>
     </row>
